--- a/data/trans_bre/IP18E_R1-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18E_R1-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-17,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-17,59%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>5.837788904695895</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.499160327984828</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.106447821982959</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-17.20078916360233</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.06536432294367504</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.02617635125918367</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.01200262934304826</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1759022408694955</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 11,36</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,29; 2,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,05; 6,18</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-35,89; -3,81</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 13,35</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-7,51; 2,22</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-4,27; 6,81</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-36,14; -4,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.2851713953680667</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.294439930095238</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.049222375075738</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-35.89239622324786</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.003246081157492484</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.07508836223409417</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.04269365483794549</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3613972859863073</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.35839593897762</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.121761503453197</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.181962974710689</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-3.81421318820779</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1334817443770797</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.02220959220302336</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.06813937655021772</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>-0.04127388627087316</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-0,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,28; 3,06</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,16; 3,93</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,83; 3,05</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-10,25; 15,93</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-4,49; 3,33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 4,25</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-3,96; 3,25</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-11,14; 20,7</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.747099548349317</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.019571196837676</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1075380571043061</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.205718665632305</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.007975743922496274</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.01071933523656047</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.001133977628949924</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.01393234070437804</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-14,39</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-14,62%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.283265786300655</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.156978050187895</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.828303173910924</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-10.2510606740178</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.04488282275452534</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.02216135967502557</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.03964205852929042</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1113725378221991</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,12; 4,29</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,31; 6,28</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 2,54</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-28,29; -4,7</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-6,4; 4,62</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-3,49; 6,9</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-5,94; 2,73</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-28,74; -5,03</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.057167991290545</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.929924069227152</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.047494763956776</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>15.9328436358746</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.03329497832648714</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.04248054315917339</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.03246529474578704</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2070048027842851</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-2,53%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.9343465495404324</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.357661397280407</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.725177745144646</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-14.38840419892193</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.009906860451272093</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.0145621046848359</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.01818917089498902</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1461704970912843</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,6; 4,11</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,98; 3,88</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,48; 6,21</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-13,97; 8,47</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-4,84; 4,52</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-4,15; 4,19</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-3,64; 6,84</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-14,68; 9,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.121704508774442</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.314262171571065</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.697749706369502</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-28.28635740644038</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.06396053054629433</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.03486204493582475</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.05936459477927653</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2873537503619633</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.293727606525207</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.275612881858875</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.537769129668745</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-4.696201994916265</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.04624203809594874</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.06903018606785608</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.02729133682268892</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>-0.05026558731736787</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.1075468930850754</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1640510361580416</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.222445056572763</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.346010085316141</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.001147630728296576</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.001735033669953822</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.01305496735438413</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.02527504499897774</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.598785428941984</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.977202548996303</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.478380834904746</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-13.97401972929868</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.04838536130812231</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.04146773545731496</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.03643978602287767</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1467657618062839</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.110536566664258</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.879693732932313</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.213663019980764</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8.468208153589103</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.04521676187851074</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.0419168085575854</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.06842737732182971</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.09513404820926306</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,38</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,06%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-7,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,01; 2,77</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 2,17</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 2,02</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,42; -0,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,14; 3,02</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-1,91; 2,31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 2,17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-14,39; -1,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.5266375541216339</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.05369189010610009</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.05993594224862342</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-7.383378255313843</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.005660364719058183</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0005671992674663736</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.0006368641605210635</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.07889630570803043</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.009945721211036</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.817154248090016</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.108879557455874</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-13.41608214260037</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.02140779879511337</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.01906950021287301</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.02219705650590035</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1438973872452231</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.770843510021321</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.169592177848933</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.024141917181573</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.8702447051016832</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.03016667033051384</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.02310519564038626</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.02171610236517124</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.009971739753965045</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
